--- a/data/trans_orig/IP07C04-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP07C04-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse  alegre en 2007 (tasa de respuesta: 89,79%)</t>
+          <t>Menores según la frecuencia de sentirse alegre en 2007 (tasa de respuesta: 89,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17148</t>
+          <t>16776</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27331</t>
+          <t>26940</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>42,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>67,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19772</t>
+          <t>20065</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28508</t>
+          <t>28466</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>39536</t>
+          <t>38532</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>53505</t>
+          <t>52731</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>70,27%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10688</t>
+          <t>10789</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20992</t>
+          <t>21193</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>53,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14347</t>
+          <t>13712</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18565</t>
+          <t>18719</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31686</t>
+          <t>32638</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>43,49%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>409</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>5968</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>719</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6211</t>
+          <t>6160</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4301</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4155</t>
+          <t>4706</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3372</t>
+          <t>2865</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3334</t>
+          <t>3301</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13577</t>
+          <t>13026</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20865</t>
+          <t>20825</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>51,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15348</t>
+          <t>15558</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23426</t>
+          <t>23507</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30943</t>
+          <t>31204</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41957</t>
+          <t>42473</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>77,68%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4363</t>
+          <t>4403</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11651</t>
+          <t>12202</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4928</t>
+          <t>4999</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12772</t>
+          <t>12668</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>11647</t>
+          <t>11041</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>22478</t>
+          <t>21787</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>39,85%</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3985</t>
+          <t>4379</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4343</t>
+          <t>4038</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14081</t>
+          <t>14606</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22612</t>
+          <t>22749</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25491</t>
+          <t>25790</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>36943</t>
+          <t>36491</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>50,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>42257</t>
+          <t>43139</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56673</t>
+          <t>57142</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>71,32%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5239</t>
+          <t>4968</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13203</t>
+          <t>12885</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10003</t>
+          <t>10212</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20792</t>
+          <t>21059</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17851</t>
+          <t>17444</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>30990</t>
+          <t>30385</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>37,93%</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4691</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1256</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7398</t>
+          <t>7813</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>2041</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9591</t>
+          <t>9143</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,41%</t>
         </is>
       </c>
     </row>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3405</t>
+          <t>3569</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4031</t>
+          <t>3442</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>3332</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3721</t>
+          <t>3796</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>46416</t>
+          <t>46387</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>61113</t>
+          <t>60897</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>47708</t>
+          <t>49300</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>61952</t>
+          <t>62461</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>99266</t>
+          <t>98808</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>119126</t>
+          <t>117789</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>70,67%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>18112</t>
+          <t>17831</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>31700</t>
+          <t>32337</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>18580</t>
+          <t>18480</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>32134</t>
+          <t>31436</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>39624</t>
+          <t>41336</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>59315</t>
+          <t>59362</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,61%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8724</t>
+          <t>9389</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>4650</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3198</t>
+          <t>2708</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10738</t>
+          <t>10323</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>535</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4902</t>
+          <t>4843</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>535</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4925</t>
+          <t>4956</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>22439</t>
+          <t>22768</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>33441</t>
+          <t>33224</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>36091</t>
+          <t>36673</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>48778</t>
+          <t>48053</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>58,62%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>62485</t>
+          <t>63081</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>78729</t>
+          <t>79175</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>57,04%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>71,59%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>12796</t>
+          <t>12787</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>23341</t>
+          <t>23040</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>11701</t>
+          <t>11965</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>23847</t>
+          <t>23140</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>27220</t>
+          <t>27525</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>42726</t>
+          <t>42844</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,74%</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3909</t>
+          <t>4548</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>680</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6183</t>
+          <t>6341</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1333</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>8008</t>
+          <t>7898</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -3804,7 +3804,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3416</t>
+          <t>3639</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3857</t>
+          <t>3809</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>20068</t>
+          <t>18921</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>29193</t>
+          <t>28874</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>14726</t>
+          <t>15129</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>23446</t>
+          <t>23332</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>47,37%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>73,05%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>36960</t>
+          <t>37139</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>50293</t>
+          <t>49533</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>53,28%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>71,06%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>7676</t>
+          <t>7584</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>16068</t>
+          <t>17047</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>6753</t>
+          <t>6743</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>15322</t>
+          <t>15304</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>16331</t>
+          <t>17300</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>28737</t>
+          <t>29059</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>41,69%</t>
         </is>
       </c>
     </row>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4231</t>
+          <t>4409</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5124</t>
+          <t>4066</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>674</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6346</t>
+          <t>6412</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3131</t>
+          <t>3715</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2503</t>
+          <t>2778</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>151885</t>
+          <t>150906</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>177178</t>
+          <t>176284</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>56,94%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>181213</t>
+          <t>179745</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>207983</t>
+          <t>204842</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>61,6%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>339385</t>
+          <t>340015</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>376514</t>
+          <t>376902</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>67,69%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>74360</t>
+          <t>75294</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>98734</t>
+          <t>100172</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>71925</t>
+          <t>73858</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>97349</t>
+          <t>97767</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>152994</t>
+          <t>155180</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>188926</t>
+          <t>190303</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>34,18%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>6624</t>
+          <t>6351</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>17228</t>
+          <t>16926</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>5378</t>
+          <t>5857</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>15137</t>
+          <t>16355</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>14441</t>
+          <t>14161</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>28348</t>
+          <t>29302</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>643</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>6109</t>
+          <t>6145</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>611</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>6193</t>
+          <t>5607</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>1901</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>9449</t>
+          <t>9118</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>4175</t>
+          <t>4541</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>3991</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse  alegre en 2012 (tasa de respuesta: 95,72%)</t>
+          <t>Menores según la frecuencia de sentirse alegre en 2012 (tasa de respuesta: 95,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16523</t>
+          <t>16600</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26407</t>
+          <t>26674</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>72,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17405</t>
+          <t>17268</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26236</t>
+          <t>26228</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>76,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36874</t>
+          <t>36482</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>50631</t>
+          <t>50165</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>51,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>70,53%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9897</t>
+          <t>9788</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19600</t>
+          <t>19547</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t>7416</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16366</t>
+          <t>16375</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19362</t>
+          <t>20331</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32930</t>
+          <t>33331</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>46,86%</t>
         </is>
       </c>
     </row>
@@ -5971,7 +5971,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2786</t>
+          <t>3195</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3295</t>
+          <t>2757</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6021,7 +6021,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3838</t>
+          <t>4266</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6056,7 +6056,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17997</t>
+          <t>18354</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26960</t>
+          <t>27076</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>56,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16407</t>
+          <t>16677</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26025</t>
+          <t>26396</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36868</t>
+          <t>37544</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>50369</t>
+          <t>50703</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>55,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>74,88%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4528</t>
+          <t>4479</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12814</t>
+          <t>12837</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9078</t>
+          <t>8707</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18696</t>
+          <t>18426</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>16225</t>
+          <t>16248</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>29438</t>
+          <t>28762</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>42,48%</t>
         </is>
       </c>
     </row>
@@ -6653,7 +6653,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6723,7 +6723,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2809</t>
+          <t>2729</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3001</t>
+          <t>2687</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3815</t>
+          <t>2937</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17663</t>
+          <t>17759</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28273</t>
+          <t>28544</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>66,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16056</t>
+          <t>15670</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24292</t>
+          <t>24502</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35558</t>
+          <t>36428</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>49746</t>
+          <t>50402</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>67,77%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13600</t>
+          <t>13079</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23647</t>
+          <t>24129</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5495</t>
+          <t>5940</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13997</t>
+          <t>14428</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>22121</t>
+          <t>21361</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35961</t>
+          <t>35770</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>48,1%</t>
         </is>
       </c>
     </row>
@@ -7335,7 +7335,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3567</t>
+          <t>3564</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7350,7 +7350,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4496</t>
+          <t>4382</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>576</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6003</t>
+          <t>4939</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2877</t>
+          <t>3560</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3218</t>
+          <t>3470</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7646,7 +7646,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>41755</t>
+          <t>41604</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>56099</t>
+          <t>57109</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>48814</t>
+          <t>49251</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>65306</t>
+          <t>64782</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>66,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>96324</t>
+          <t>96005</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>117502</t>
+          <t>117693</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>52,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>64,56%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>26311</t>
+          <t>25048</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>40277</t>
+          <t>40188</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>26170</t>
+          <t>25713</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>41659</t>
+          <t>41235</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>55837</t>
+          <t>55408</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>76562</t>
+          <t>76779</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>42,12%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>429</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5152</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8032,7 +8032,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2576</t>
+          <t>2453</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9799</t>
+          <t>9774</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3466</t>
+          <t>3690</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>12092</t>
+          <t>12256</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -8165,7 +8165,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4228</t>
+          <t>4126</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8180,7 +8180,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8200,7 +8200,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3616</t>
+          <t>3974</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8215,7 +8215,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -8243,7 +8243,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6236</t>
+          <t>4168</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8278,7 +8278,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3931</t>
+          <t>4073</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8313,7 +8313,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4852</t>
+          <t>4959</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>37582</t>
+          <t>37239</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>52373</t>
+          <t>51946</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>68,97%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>36118</t>
+          <t>36185</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>49520</t>
+          <t>50161</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>70,28%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>79288</t>
+          <t>77487</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>98950</t>
+          <t>98191</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>52,82%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>66,93%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>18411</t>
+          <t>18786</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>32452</t>
+          <t>32591</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>21489</t>
+          <t>20497</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>34730</t>
+          <t>34356</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>43011</t>
+          <t>43271</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>62601</t>
+          <t>63159</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>43,05%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>642</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6845</t>
+          <t>6247</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>699</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6889</t>
+          <t>6130</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>595</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6431</t>
+          <t>6509</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8827,7 +8827,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>596</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>7096</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>3103</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3806</t>
+          <t>3825</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>7307</t>
+          <t>7301</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>15313</t>
+          <t>14759</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>62,8%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>16230</t>
+          <t>15930</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>25485</t>
+          <t>25894</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>25995</t>
+          <t>25042</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>38213</t>
+          <t>37838</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>64,3%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6046</t>
+          <t>6599</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>14352</t>
+          <t>14199</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>8193</t>
+          <t>7619</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>17643</t>
+          <t>17281</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>16145</t>
+          <t>16771</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>28492</t>
+          <t>28989</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>48,42%</t>
+          <t>49,26%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>627</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5680</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4105</t>
+          <t>4740</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1397</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>7775</t>
+          <t>7669</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,03%</t>
         </is>
       </c>
     </row>
@@ -9564,7 +9564,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3889</t>
+          <t>3537</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9579,7 +9579,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>160692</t>
+          <t>159062</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>187970</t>
+          <t>186497</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>63,02%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>170542</t>
+          <t>171058</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>198628</t>
+          <t>197969</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>338867</t>
+          <t>338167</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>378929</t>
+          <t>377560</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>62,82%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>94746</t>
+          <t>96619</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>121938</t>
+          <t>124001</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>94459</t>
+          <t>96176</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>123066</t>
+          <t>121295</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>197036</t>
+          <t>198928</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>238769</t>
+          <t>238273</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>39,64%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>4742</t>
+          <t>4401</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>14021</t>
+          <t>13916</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,47 +10073,47 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>4,7%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>8427</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>4884</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>13813</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>2,76%</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
           <t>1,6%</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>4,74%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>8427</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>4430</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>13590</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>2,76%</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>11530</t>
+          <t>11563</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>24170</t>
+          <t>24322</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -10176,7 +10176,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>7168</t>
+          <t>6218</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>575</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>5958</t>
+          <t>5208</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1734</t>
+          <t>1523</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>8662</t>
+          <t>8558</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>594</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>5802</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10324,7 +10324,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>5325</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>1237</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>7572</t>
+          <t>7818</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse  alegre en 2016 (tasa de respuesta: 95,77%)</t>
+          <t>Menores según la frecuencia de sentirse alegre en 2016 (tasa de respuesta: 95,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18533</t>
+          <t>18784</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27040</t>
+          <t>27546</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20394</t>
+          <t>20205</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29298</t>
+          <t>29531</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,34%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41858</t>
+          <t>41968</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>54005</t>
+          <t>54888</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>59,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>78,36%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4142</t>
+          <t>4258</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12108</t>
+          <t>12465</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8230</t>
+          <t>7997</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17134</t>
+          <t>17323</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14762</t>
+          <t>13986</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26885</t>
+          <t>26462</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>37,78%</t>
         </is>
       </c>
     </row>
@@ -10979,7 +10979,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4274</t>
+          <t>4992</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10994,7 +10994,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11049,7 +11049,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4642</t>
+          <t>4271</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18513</t>
+          <t>18672</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30532</t>
+          <t>30337</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>61,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25950</t>
+          <t>26418</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36661</t>
+          <t>37501</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47864</t>
+          <t>48245</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63593</t>
+          <t>64621</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>66,63%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15909</t>
+          <t>16319</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27327</t>
+          <t>27464</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10487</t>
+          <t>9406</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21200</t>
+          <t>20913</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>29083</t>
+          <t>29033</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>44714</t>
+          <t>44866</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>46,26%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>1161</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7366</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3114</t>
+          <t>3001</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11711,7 +11711,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1750</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8723</t>
+          <t>8625</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,89%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11275</t>
+          <t>11118</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19863</t>
+          <t>19974</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>72,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15640</t>
+          <t>15522</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26372</t>
+          <t>26115</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29601</t>
+          <t>29685</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43294</t>
+          <t>42842</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>63,51%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6619</t>
+          <t>6311</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14966</t>
+          <t>15167</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12626</t>
+          <t>12291</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23038</t>
+          <t>22908</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21300</t>
+          <t>21775</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>34754</t>
+          <t>34702</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>51,44%</t>
         </is>
       </c>
     </row>
@@ -12343,7 +12343,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5074</t>
+          <t>6006</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12358,7 +12358,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12378,7 +12378,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4942</t>
+          <t>4520</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>986</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7024</t>
+          <t>8030</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>11,9%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>56010</t>
+          <t>55549</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>73277</t>
+          <t>72199</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>52798</t>
+          <t>53362</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>69691</t>
+          <t>69434</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>113815</t>
+          <t>114465</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>137609</t>
+          <t>138388</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>65,87%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>33244</t>
+          <t>34211</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>50444</t>
+          <t>50734</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>25003</t>
+          <t>25523</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>41322</t>
+          <t>41601</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>63338</t>
+          <t>62853</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>87677</t>
+          <t>86842</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>41,34%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2557</t>
+          <t>2520</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9420</t>
+          <t>9786</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1479</t>
+          <t>1438</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8143</t>
+          <t>8156</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4883</t>
+          <t>5008</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>15041</t>
+          <t>15331</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -13173,7 +13173,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4313</t>
+          <t>3827</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13208,7 +13208,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4154</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>37681</t>
+          <t>37187</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>50943</t>
+          <t>51707</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>32462</t>
+          <t>33023</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>46029</t>
+          <t>46571</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>74521</t>
+          <t>74536</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>94392</t>
+          <t>94026</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>65,17%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>20949</t>
+          <t>20263</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>34170</t>
+          <t>34685</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>20156</t>
+          <t>20157</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>33128</t>
+          <t>32703</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13644,7 +13644,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>43046</t>
+          <t>43064</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>62483</t>
+          <t>63012</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,68%</t>
         </is>
       </c>
     </row>
@@ -13707,7 +13707,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4488</t>
+          <t>5206</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13722,7 +13722,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>860</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6850</t>
+          <t>6736</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1327</t>
+          <t>1852</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>8810</t>
+          <t>8873</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -13820,7 +13820,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2625</t>
+          <t>3072</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13835,7 +13835,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13890,7 +13890,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3019</t>
+          <t>2696</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13905,7 +13905,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -13933,7 +13933,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3847</t>
+          <t>3798</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13948,7 +13948,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13968,7 +13968,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4798</t>
+          <t>4634</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13983,7 +13983,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>724</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5961</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14013,12 +14013,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>14185</t>
+          <t>13971</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>24098</t>
+          <t>23304</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>69,86%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>17834</t>
+          <t>18138</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>27755</t>
+          <t>27958</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>48,82%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>35274</t>
+          <t>35041</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>48325</t>
+          <t>47874</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>67,89%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>8314</t>
+          <t>8666</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>17799</t>
+          <t>18216</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>8724</t>
+          <t>8359</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>18383</t>
+          <t>18218</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>20137</t>
+          <t>20399</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>33505</t>
+          <t>33157</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,02%</t>
         </is>
       </c>
     </row>
@@ -14389,7 +14389,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4309</t>
+          <t>4608</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14404,7 +14404,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14424,7 +14424,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4353</t>
+          <t>3793</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14439,7 +14439,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>685</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5897</t>
+          <t>6352</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14474,7 +14474,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>9,01%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>178269</t>
+          <t>177282</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>207691</t>
+          <t>205975</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>54,34%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>63,31%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>185236</t>
+          <t>186399</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>215760</t>
+          <t>215813</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>65,12%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>372463</t>
+          <t>372390</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>415008</t>
+          <t>414416</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>62,94%</t>
+          <t>62,85%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>105935</t>
+          <t>106691</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>135378</t>
+          <t>135315</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>104334</t>
+          <t>104576</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>132327</t>
+          <t>132717</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>216937</t>
+          <t>218564</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>259236</t>
+          <t>260049</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>39,44%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>8979</t>
+          <t>9230</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>21127</t>
+          <t>21439</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>5237</t>
+          <t>5382</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>16095</t>
+          <t>16119</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>17175</t>
+          <t>16536</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>32257</t>
+          <t>33291</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -15184,7 +15184,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2670</t>
+          <t>2635</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15199,7 +15199,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15219,7 +15219,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>4131</t>
+          <t>4689</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15234,7 +15234,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15254,7 +15254,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>4870</t>
+          <t>4881</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15297,7 +15297,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>3826</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15312,7 +15312,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15332,7 +15332,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>5262</t>
+          <t>5205</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15347,7 +15347,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>721</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>6066</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15382,7 +15382,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
